--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -36,15 +36,15 @@
     <t xml:space="preserve">Arica y Parinacota</t>
   </si>
   <si>
+    <t xml:space="preserve">Camarones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
-    <t xml:space="preserve">Camarones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Lagos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>15201</v>
+        <v>15102</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-35</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="3">
@@ -498,13 +498,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15102</v>
+        <v>15202</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-41</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="4">
@@ -515,13 +515,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15202</v>
+        <v>15201</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-61</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-3158</v>
+        <v>-214</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
